--- a/data/gravel/Merida Silex 2025.xlsx
+++ b/data/gravel/Merida Silex 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8B5AB9C-2CA7-804F-9768-AA35E086CE11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8502FB83-477D-F84C-898C-B058C31929CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31620" yWindow="-26720" windowWidth="27200" windowHeight="19560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7120" yWindow="920" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="104">
   <si>
     <t>brand</t>
   </si>
@@ -326,9 +326,6 @@
     <t>Silex</t>
   </si>
   <si>
-    <t>https://www.merida-bikes.com/en/bike/5662/silex-9000</t>
-  </si>
-  <si>
     <t>handlebar_width</t>
   </si>
   <si>
@@ -342,6 +339,12 @@
   </si>
   <si>
     <t>a8:h33</t>
+  </si>
+  <si>
+    <t>https://www.merida-bikes.com/en/bikefinder/tag/silex-48/root/bikes-subcategory</t>
+  </si>
+  <si>
+    <t>https://d27bpu3c1nsd28.cloudfront.net/merida-v2/crud-zoom-img/master/bikes/2026/SILEX_9000_grnbrn_MY26.tif?p1</t>
   </si>
 </sst>
 </file>
@@ -757,7 +760,12 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>97</v>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:61" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:61" x14ac:dyDescent="0.3">
@@ -765,7 +773,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
@@ -1382,31 +1390,31 @@
     </row>
     <row r="23" spans="1:35" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B23" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="24" spans="1:35" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25" spans="1:35" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:35" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:35" x14ac:dyDescent="0.3">
